--- a/ussd-api-master/Documentations/countryList.xlsx
+++ b/ussd-api-master/Documentations/countryList.xlsx
@@ -5,16 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eclipse-workspace\workspace1\ussd-api-master\Documentations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspaces\workspace1\ussd-api-master\ussd-api-master\Documentations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3659866-0939-4A21-A0A2-D27D4F629B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641207C1-2CCA-4083-9B50-313622801D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{47B715E9-E7F4-41FB-8459-15FB7DB0CB70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{47B715E9-E7F4-41FB-8459-15FB7DB0CB70}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="466">
   <si>
     <t>United States</t>
   </si>
@@ -1435,715 +1434,19 @@
   </si>
   <si>
     <t xml:space="preserve"> WHERE NOT EXISTS ( SELECT 1 FROM country WHERE  country_code =  </t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','United States','US');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','United Kingdom','GB');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Canada','CA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Australia','AU');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Afghanistan','AF');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Albania','AL');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Algeria','DZ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','American Samoa','AS');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Andorra','AD');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Angola','AO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Anguilla','AI');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Antarctica','AQ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Antigua and Barbuda ','AG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Argentina','AR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Armenia','AM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Aruba','AW');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Austria','AT');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Azerbaijan','AZ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Bahamas','BS');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Bahrain','BH');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Bangladesh','BD');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Barbados','BB');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Belarus','BY');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Belgium','BE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Belize','BZ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Benin','BJ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Bermuda','BM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Bhutan','BT');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Bolivia','BO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Bosnia and Herzegovina','BA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Botswana','BW');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Brazil','BR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','British Indian Ocean','IO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Brunei','BN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Bulgaria','BG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Burkina Faso','BF');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Burma (Myanmar)','MM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Burundi','BI');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Cambodia','KH');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Cameroon','CM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Cape Verde','CV');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Cayman Islands','KY');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Central African Republic','CF');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Chad','TD');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Chile','CL');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','China','CN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Christmas Island','CX');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Cocos (Keeling) Islands','CC');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Colombia','CO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Comoros','KM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Congo, Democratic Republic of the','CD');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Congo, Republic of the','CG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Cook Islands','CK');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Costa Rica','CR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Croatia','HR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Cyprus','CY');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Czech Republic','CZ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Denmark','DK');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Djibouti','DJ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Dominica','DM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Dominican Republic','DO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','East Timor','TL');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Ecuador','EC');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Egypt','EG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','El Salvador','SV');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Equatorial Guinea','GQ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Eritrea','ER');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Estonia','EE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Ethiopia','ET');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Falkland Islands (Malvinas)','FK');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Faroe Islands','FO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Fiji','FJ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Finland','FI');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','France','FR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','French Guiana','GF');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','French Polynesia','PF');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Gabon','GA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Gambia','GM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Georgia','GE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Germany','DE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Ghana','GH');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Gibraltar','GI');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Greece','GR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Greenland','GL');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Grenada','GD');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Guadeloupe','GP');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Guam','GU');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Guatemala','GT');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Guinea','GN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Guinea-Bissau','GW');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Guyana','GY');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Haiti','HT');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Honduras','HN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Hong Kong','HK');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Hungary','HU');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Iceland','IS');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','India','IN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Indonesia','ID');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Iraq','IQ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Ireland','IE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Israel','IL');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Italy','IT');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Ivory Coast','CI');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Jamaica','JM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Japan','JP');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Jordan','JO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Kazakhstan','KZ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Kenya','KE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Kiribati','KI');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Korea, South','KR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Kuwait','KW');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Kyrgyzstan','KG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Laos','LA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Latvia','LV');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Lebanon','LB');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Lesotho','LS');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Liberia','LR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Liechtenstein','LI');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Lithuania','LT');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Luxembourg','LU');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Macau','MO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Macedonia, Republic of','MK');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Madagascar','MG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Malawi','MW');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Malaysia','MY');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Maldives','MV');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Mali','ML');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Malta','MT');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Marshall Islands','MH');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Martinique','MQ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Mauritania','MR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Mauritius','MU');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Mayotte','YT');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Mexico','MX');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Micronesia','FM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Moldova','MD');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Monaco','MC');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Mongolia','MN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Montserrat','MS');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Morocco','MA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Mozambique','MZ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Namibia','NA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Nauru','NR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Nepal','NP');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Netherlands','NL');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Netherlands Antilles','AN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','New Caledonia','NC');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','New Zealand','NZ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Nicaragua','NI');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Niger','NE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Nigeria','NG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Niue','NU');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Norfolk Island','NF');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Northern Mariana Islands','MP');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Norway','NO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Oman','OM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Pakistan','PK');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Palau','PW');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Palestinian Territory','PS');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Panama','PA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Papua New Guinea','PG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Paraguay','PY');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Peru','PE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Philippines','PH');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Pitcairn Island','PN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Poland','PL');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Portugal','PT');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Puerto Rico','PR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Qatar','QA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Reunion','RE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Romania','RO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Russia','RU');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Rwanda','RW');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Saint Helena','SH');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Saint Kitts and Nevis','KN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Saint Lucia','LC');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Saint Pierre and Miquelon','PM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Saint Vincent and the Grenadines','VC');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Samoa','WS');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','San Marino','SM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Sao Tome and Principe','ST');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Saudi Arabia','SA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Senegal','SN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Serbia and Montenegro','CS');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Seychelles','SC');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Sierra Leone','SL');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Singapore','SG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Slovakia','SK');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Slovenia','SI');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Solomon Islands','SB');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Somalia','SO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','South Africa','ZA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','South Georgia and the South Sandwich Islands','GS');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Spain','ES');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Sri Lanka','LK');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Suriname','SR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Svalbard and Jan Mayen','SJ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Swaziland','SZ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Sweden','SE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Switzerland','CH');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Taiwan','TW');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Tajikistan','TJ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Tanzania','TZ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Thailand','TH');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Togo','TG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Tokelau','TK');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Tonga','TO');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Trinidad and Tobago','TT');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Tunisia','TN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Turkey','TR');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Turkmenistan','TM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Turks and Caicos Islands','TC');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Tuvalu','TV');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Uganda','UG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Ukraine','UA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','United Arab Emirates','AE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','United States Minor Outlying Islands','UM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Uruguay','UY');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Uzbekistan','UZ');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Vanuatu','VU');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Vatican City','VA');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Venezuela','VE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Vietnam','VN');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Virgin Islands, British','VG');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Virgin Islands, U. S.','VI');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Wallis and Futuna','WF');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Western Sahara','EH');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Yemen','YE');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Zambia','ZM');</t>
-  </si>
-  <si>
-    <t>INSERT INTO country values('','Zimbabw','ZW');</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2166,11 +1469,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2495,6 +1795,8 @@
     <col min="4" max="5" width="5.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" customWidth="1"/>
     <col min="7" max="7" width="25.5703125" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="57.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2508,10 +1810,10 @@
       <c r="C1" t="s">
         <v>465</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F1" t="s">
@@ -2538,10 +1840,10 @@
       <c r="C2" t="s">
         <v>465</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F2" t="s">
@@ -2568,10 +1870,10 @@
       <c r="C3" t="s">
         <v>465</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F3" t="s">
@@ -2598,10 +1900,10 @@
       <c r="C4" t="s">
         <v>465</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F4" t="s">
@@ -2628,10 +1930,10 @@
       <c r="C5" t="s">
         <v>465</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F5" t="s">
@@ -2658,10 +1960,10 @@
       <c r="C6" t="s">
         <v>465</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F6" t="s">
@@ -2688,10 +1990,10 @@
       <c r="C7" t="s">
         <v>465</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F7" t="s">
@@ -2718,10 +2020,10 @@
       <c r="C8" t="s">
         <v>465</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D8" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F8" t="s">
@@ -2748,10 +2050,10 @@
       <c r="C9" t="s">
         <v>465</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F9" t="s">
@@ -2778,10 +2080,10 @@
       <c r="C10" t="s">
         <v>465</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F10" t="s">
@@ -2808,10 +2110,10 @@
       <c r="C11" t="s">
         <v>465</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F11" t="s">
@@ -2838,10 +2140,10 @@
       <c r="C12" t="s">
         <v>465</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="D12" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F12" t="s">
@@ -2868,10 +2170,10 @@
       <c r="C13" t="s">
         <v>465</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D13" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F13" t="s">
@@ -2898,10 +2200,10 @@
       <c r="C14" t="s">
         <v>465</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="D14" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F14" t="s">
@@ -2928,10 +2230,10 @@
       <c r="C15" t="s">
         <v>465</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="D15" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F15" t="s">
@@ -2958,10 +2260,10 @@
       <c r="C16" t="s">
         <v>465</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="D16" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F16" t="s">
@@ -2988,10 +2290,10 @@
       <c r="C17" t="s">
         <v>465</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="D17" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F17" t="s">
@@ -3018,10 +2320,10 @@
       <c r="C18" t="s">
         <v>465</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="D18" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F18" t="s">
@@ -3048,10 +2350,10 @@
       <c r="C19" t="s">
         <v>465</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="D19" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F19" t="s">
@@ -3078,10 +2380,10 @@
       <c r="C20" t="s">
         <v>465</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="D20" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F20" t="s">
@@ -3108,10 +2410,10 @@
       <c r="C21" t="s">
         <v>465</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="D21" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F21" t="s">
@@ -3138,10 +2440,10 @@
       <c r="C22" t="s">
         <v>465</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="D22" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F22" t="s">
@@ -3168,10 +2470,10 @@
       <c r="C23" t="s">
         <v>465</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="D23" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F23" t="s">
@@ -3198,10 +2500,10 @@
       <c r="C24" t="s">
         <v>465</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="D24" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F24" t="s">
@@ -3228,10 +2530,10 @@
       <c r="C25" t="s">
         <v>465</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F25" t="s">
@@ -3258,10 +2560,10 @@
       <c r="C26" t="s">
         <v>465</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="D26" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F26" t="s">
@@ -3288,10 +2590,10 @@
       <c r="C27" t="s">
         <v>465</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="D27" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F27" t="s">
@@ -3318,10 +2620,10 @@
       <c r="C28" t="s">
         <v>465</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="D28" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F28" t="s">
@@ -3348,10 +2650,10 @@
       <c r="C29" t="s">
         <v>465</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="D29" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F29" t="s">
@@ -3378,10 +2680,10 @@
       <c r="C30" t="s">
         <v>465</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="D30" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F30" t="s">
@@ -3408,10 +2710,10 @@
       <c r="C31" t="s">
         <v>465</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="D31" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F31" t="s">
@@ -3438,10 +2740,10 @@
       <c r="C32" t="s">
         <v>465</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="D32" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F32" t="s">
@@ -3468,10 +2770,10 @@
       <c r="C33" t="s">
         <v>465</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="D33" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F33" t="s">
@@ -3498,10 +2800,10 @@
       <c r="C34" t="s">
         <v>465</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E34" s="2" t="s">
+      <c r="D34" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F34" t="s">
@@ -3528,10 +2830,10 @@
       <c r="C35" t="s">
         <v>465</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="D35" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F35" t="s">
@@ -3558,10 +2860,10 @@
       <c r="C36" t="s">
         <v>465</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="D36" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F36" t="s">
@@ -3588,10 +2890,10 @@
       <c r="C37" t="s">
         <v>465</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="D37" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F37" t="s">
@@ -3618,10 +2920,10 @@
       <c r="C38" t="s">
         <v>465</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E38" s="2" t="s">
+      <c r="D38" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F38" t="s">
@@ -3648,10 +2950,10 @@
       <c r="C39" t="s">
         <v>465</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="D39" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F39" t="s">
@@ -3678,10 +2980,10 @@
       <c r="C40" t="s">
         <v>465</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E40" s="2" t="s">
+      <c r="D40" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F40" t="s">
@@ -3708,10 +3010,10 @@
       <c r="C41" t="s">
         <v>465</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E41" s="2" t="s">
+      <c r="D41" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F41" t="s">
@@ -3738,10 +3040,10 @@
       <c r="C42" t="s">
         <v>465</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E42" s="2" t="s">
+      <c r="D42" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F42" t="s">
@@ -3768,10 +3070,10 @@
       <c r="C43" t="s">
         <v>465</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E43" s="2" t="s">
+      <c r="D43" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F43" t="s">
@@ -3798,10 +3100,10 @@
       <c r="C44" t="s">
         <v>465</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E44" s="2" t="s">
+      <c r="D44" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F44" t="s">
@@ -3828,10 +3130,10 @@
       <c r="C45" t="s">
         <v>465</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E45" s="2" t="s">
+      <c r="D45" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F45" t="s">
@@ -3858,10 +3160,10 @@
       <c r="C46" t="s">
         <v>465</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E46" s="2" t="s">
+      <c r="D46" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F46" t="s">
@@ -3888,10 +3190,10 @@
       <c r="C47" t="s">
         <v>465</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E47" s="2" t="s">
+      <c r="D47" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F47" t="s">
@@ -3918,10 +3220,10 @@
       <c r="C48" t="s">
         <v>465</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E48" s="2" t="s">
+      <c r="D48" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F48" t="s">
@@ -3948,10 +3250,10 @@
       <c r="C49" t="s">
         <v>465</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="D49" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F49" t="s">
@@ -3978,10 +3280,10 @@
       <c r="C50" t="s">
         <v>465</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E50" s="2" t="s">
+      <c r="D50" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F50" t="s">
@@ -4008,10 +3310,10 @@
       <c r="C51" t="s">
         <v>465</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E51" s="2" t="s">
+      <c r="D51" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F51" t="s">
@@ -4038,10 +3340,10 @@
       <c r="C52" t="s">
         <v>465</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E52" s="2" t="s">
+      <c r="D52" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F52" t="s">
@@ -4068,10 +3370,10 @@
       <c r="C53" t="s">
         <v>465</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="D53" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F53" t="s">
@@ -4098,10 +3400,10 @@
       <c r="C54" t="s">
         <v>465</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="D54" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F54" t="s">
@@ -4128,10 +3430,10 @@
       <c r="C55" t="s">
         <v>465</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="D55" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F55" t="s">
@@ -4158,10 +3460,10 @@
       <c r="C56" t="s">
         <v>465</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="D56" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F56" t="s">
@@ -4188,10 +3490,10 @@
       <c r="C57" t="s">
         <v>465</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E57" s="2" t="s">
+      <c r="D57" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F57" t="s">
@@ -4218,10 +3520,10 @@
       <c r="C58" t="s">
         <v>465</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="D58" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F58" t="s">
@@ -4248,10 +3550,10 @@
       <c r="C59" t="s">
         <v>465</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E59" s="2" t="s">
+      <c r="D59" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F59" t="s">
@@ -4278,10 +3580,10 @@
       <c r="C60" t="s">
         <v>465</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E60" s="2" t="s">
+      <c r="D60" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F60" t="s">
@@ -4308,10 +3610,10 @@
       <c r="C61" t="s">
         <v>465</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E61" s="2" t="s">
+      <c r="D61" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F61" t="s">
@@ -4338,10 +3640,10 @@
       <c r="C62" t="s">
         <v>465</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E62" s="2" t="s">
+      <c r="D62" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F62" t="s">
@@ -4368,10 +3670,10 @@
       <c r="C63" t="s">
         <v>465</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="D63" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F63" t="s">
@@ -4398,10 +3700,10 @@
       <c r="C64" t="s">
         <v>465</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="D64" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F64" t="s">
@@ -4428,10 +3730,10 @@
       <c r="C65" t="s">
         <v>465</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="D65" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F65" t="s">
@@ -4458,10 +3760,10 @@
       <c r="C66" t="s">
         <v>465</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="D66" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F66" t="s">
@@ -4488,10 +3790,10 @@
       <c r="C67" t="s">
         <v>465</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E67" s="2" t="s">
+      <c r="D67" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F67" t="s">
@@ -4518,10 +3820,10 @@
       <c r="C68" t="s">
         <v>465</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E68" s="2" t="s">
+      <c r="D68" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F68" t="s">
@@ -4548,10 +3850,10 @@
       <c r="C69" t="s">
         <v>465</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E69" s="2" t="s">
+      <c r="D69" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F69" t="s">
@@ -4578,10 +3880,10 @@
       <c r="C70" t="s">
         <v>465</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E70" s="2" t="s">
+      <c r="D70" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F70" t="s">
@@ -4608,10 +3910,10 @@
       <c r="C71" t="s">
         <v>465</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E71" s="2" t="s">
+      <c r="D71" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F71" t="s">
@@ -4638,10 +3940,10 @@
       <c r="C72" t="s">
         <v>465</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E72" s="2" t="s">
+      <c r="D72" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F72" t="s">
@@ -4668,10 +3970,10 @@
       <c r="C73" t="s">
         <v>465</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E73" s="2" t="s">
+      <c r="D73" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F73" t="s">
@@ -4698,10 +4000,10 @@
       <c r="C74" t="s">
         <v>465</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E74" s="2" t="s">
+      <c r="D74" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F74" t="s">
@@ -4728,10 +4030,10 @@
       <c r="C75" t="s">
         <v>465</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E75" s="2" t="s">
+      <c r="D75" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F75" t="s">
@@ -4758,10 +4060,10 @@
       <c r="C76" t="s">
         <v>465</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E76" s="2" t="s">
+      <c r="D76" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F76" t="s">
@@ -4788,10 +4090,10 @@
       <c r="C77" t="s">
         <v>465</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E77" s="2" t="s">
+      <c r="D77" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F77" t="s">
@@ -4818,10 +4120,10 @@
       <c r="C78" t="s">
         <v>465</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E78" s="2" t="s">
+      <c r="D78" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F78" t="s">
@@ -4848,10 +4150,10 @@
       <c r="C79" t="s">
         <v>465</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E79" s="2" t="s">
+      <c r="D79" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F79" t="s">
@@ -4878,10 +4180,10 @@
       <c r="C80" t="s">
         <v>465</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E80" s="2" t="s">
+      <c r="D80" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F80" t="s">
@@ -4908,10 +4210,10 @@
       <c r="C81" t="s">
         <v>465</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E81" s="2" t="s">
+      <c r="D81" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F81" t="s">
@@ -4938,10 +4240,10 @@
       <c r="C82" t="s">
         <v>465</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E82" s="2" t="s">
+      <c r="D82" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F82" t="s">
@@ -4968,10 +4270,10 @@
       <c r="C83" t="s">
         <v>465</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E83" s="2" t="s">
+      <c r="D83" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F83" t="s">
@@ -4998,10 +4300,10 @@
       <c r="C84" t="s">
         <v>465</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E84" s="2" t="s">
+      <c r="D84" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F84" t="s">
@@ -5028,10 +4330,10 @@
       <c r="C85" t="s">
         <v>465</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E85" s="2" t="s">
+      <c r="D85" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F85" t="s">
@@ -5058,10 +4360,10 @@
       <c r="C86" t="s">
         <v>465</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E86" s="2" t="s">
+      <c r="D86" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F86" t="s">
@@ -5088,10 +4390,10 @@
       <c r="C87" t="s">
         <v>465</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E87" s="2" t="s">
+      <c r="D87" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F87" t="s">
@@ -5118,10 +4420,10 @@
       <c r="C88" t="s">
         <v>465</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E88" s="2" t="s">
+      <c r="D88" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F88" t="s">
@@ -5148,10 +4450,10 @@
       <c r="C89" t="s">
         <v>465</v>
       </c>
-      <c r="D89" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E89" s="2" t="s">
+      <c r="D89" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F89" t="s">
@@ -5178,10 +4480,10 @@
       <c r="C90" t="s">
         <v>465</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E90" s="2" t="s">
+      <c r="D90" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F90" t="s">
@@ -5208,10 +4510,10 @@
       <c r="C91" t="s">
         <v>465</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E91" s="2" t="s">
+      <c r="D91" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F91" t="s">
@@ -5238,10 +4540,10 @@
       <c r="C92" t="s">
         <v>465</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E92" s="2" t="s">
+      <c r="D92" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F92" t="s">
@@ -5268,10 +4570,10 @@
       <c r="C93" t="s">
         <v>465</v>
       </c>
-      <c r="D93" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E93" s="2" t="s">
+      <c r="D93" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F93" t="s">
@@ -5298,10 +4600,10 @@
       <c r="C94" t="s">
         <v>465</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E94" s="2" t="s">
+      <c r="D94" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F94" t="s">
@@ -5328,10 +4630,10 @@
       <c r="C95" t="s">
         <v>465</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E95" s="2" t="s">
+      <c r="D95" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F95" t="s">
@@ -5358,10 +4660,10 @@
       <c r="C96" t="s">
         <v>465</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E96" s="2" t="s">
+      <c r="D96" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F96" t="s">
@@ -5388,10 +4690,10 @@
       <c r="C97" t="s">
         <v>465</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E97" s="2" t="s">
+      <c r="D97" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F97" t="s">
@@ -5418,10 +4720,10 @@
       <c r="C98" t="s">
         <v>465</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E98" s="2" t="s">
+      <c r="D98" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F98" t="s">
@@ -5448,10 +4750,10 @@
       <c r="C99" t="s">
         <v>465</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E99" s="2" t="s">
+      <c r="D99" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F99" t="s">
@@ -5478,10 +4780,10 @@
       <c r="C100" t="s">
         <v>465</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E100" s="2" t="s">
+      <c r="D100" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F100" t="s">
@@ -5508,10 +4810,10 @@
       <c r="C101" t="s">
         <v>465</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E101" s="2" t="s">
+      <c r="D101" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F101" t="s">
@@ -5538,10 +4840,10 @@
       <c r="C102" t="s">
         <v>465</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E102" s="2" t="s">
+      <c r="D102" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F102" t="s">
@@ -5568,10 +4870,10 @@
       <c r="C103" t="s">
         <v>465</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E103" s="2" t="s">
+      <c r="D103" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F103" t="s">
@@ -5598,10 +4900,10 @@
       <c r="C104" t="s">
         <v>465</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E104" s="2" t="s">
+      <c r="D104" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F104" t="s">
@@ -5628,10 +4930,10 @@
       <c r="C105" t="s">
         <v>465</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E105" s="2" t="s">
+      <c r="D105" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F105" t="s">
@@ -5658,10 +4960,10 @@
       <c r="C106" t="s">
         <v>465</v>
       </c>
-      <c r="D106" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E106" s="2" t="s">
+      <c r="D106" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F106" t="s">
@@ -5688,10 +4990,10 @@
       <c r="C107" t="s">
         <v>465</v>
       </c>
-      <c r="D107" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E107" s="2" t="s">
+      <c r="D107" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F107" t="s">
@@ -5718,10 +5020,10 @@
       <c r="C108" t="s">
         <v>465</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E108" s="2" t="s">
+      <c r="D108" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F108" t="s">
@@ -5748,10 +5050,10 @@
       <c r="C109" t="s">
         <v>465</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E109" s="2" t="s">
+      <c r="D109" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F109" t="s">
@@ -5778,10 +5080,10 @@
       <c r="C110" t="s">
         <v>465</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E110" s="2" t="s">
+      <c r="D110" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F110" t="s">
@@ -5808,10 +5110,10 @@
       <c r="C111" t="s">
         <v>465</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E111" s="2" t="s">
+      <c r="D111" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F111" t="s">
@@ -5838,10 +5140,10 @@
       <c r="C112" t="s">
         <v>465</v>
       </c>
-      <c r="D112" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E112" s="2" t="s">
+      <c r="D112" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F112" t="s">
@@ -5868,10 +5170,10 @@
       <c r="C113" t="s">
         <v>465</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E113" s="2" t="s">
+      <c r="D113" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F113" t="s">
@@ -5898,10 +5200,10 @@
       <c r="C114" t="s">
         <v>465</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E114" s="2" t="s">
+      <c r="D114" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F114" t="s">
@@ -5928,10 +5230,10 @@
       <c r="C115" t="s">
         <v>465</v>
       </c>
-      <c r="D115" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E115" s="2" t="s">
+      <c r="D115" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F115" t="s">
@@ -5958,10 +5260,10 @@
       <c r="C116" t="s">
         <v>465</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E116" s="2" t="s">
+      <c r="D116" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F116" t="s">
@@ -5988,10 +5290,10 @@
       <c r="C117" t="s">
         <v>465</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E117" s="2" t="s">
+      <c r="D117" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E117" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F117" t="s">
@@ -6018,10 +5320,10 @@
       <c r="C118" t="s">
         <v>465</v>
       </c>
-      <c r="D118" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E118" s="2" t="s">
+      <c r="D118" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E118" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F118" t="s">
@@ -6048,10 +5350,10 @@
       <c r="C119" t="s">
         <v>465</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E119" s="2" t="s">
+      <c r="D119" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F119" t="s">
@@ -6078,10 +5380,10 @@
       <c r="C120" t="s">
         <v>465</v>
       </c>
-      <c r="D120" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E120" s="2" t="s">
+      <c r="D120" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F120" t="s">
@@ -6108,10 +5410,10 @@
       <c r="C121" t="s">
         <v>465</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E121" s="2" t="s">
+      <c r="D121" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F121" t="s">
@@ -6138,10 +5440,10 @@
       <c r="C122" t="s">
         <v>465</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E122" s="2" t="s">
+      <c r="D122" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F122" t="s">
@@ -6168,10 +5470,10 @@
       <c r="C123" t="s">
         <v>465</v>
       </c>
-      <c r="D123" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E123" s="2" t="s">
+      <c r="D123" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F123" t="s">
@@ -6198,10 +5500,10 @@
       <c r="C124" t="s">
         <v>465</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E124" s="2" t="s">
+      <c r="D124" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F124" t="s">
@@ -6228,10 +5530,10 @@
       <c r="C125" t="s">
         <v>465</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E125" s="2" t="s">
+      <c r="D125" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F125" t="s">
@@ -6258,10 +5560,10 @@
       <c r="C126" t="s">
         <v>465</v>
       </c>
-      <c r="D126" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E126" s="2" t="s">
+      <c r="D126" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E126" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F126" t="s">
@@ -6288,10 +5590,10 @@
       <c r="C127" t="s">
         <v>465</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E127" s="2" t="s">
+      <c r="D127" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E127" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F127" t="s">
@@ -6318,10 +5620,10 @@
       <c r="C128" t="s">
         <v>465</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E128" s="2" t="s">
+      <c r="D128" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F128" t="s">
@@ -6348,10 +5650,10 @@
       <c r="C129" t="s">
         <v>465</v>
       </c>
-      <c r="D129" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E129" s="2" t="s">
+      <c r="D129" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F129" t="s">
@@ -6378,10 +5680,10 @@
       <c r="C130" t="s">
         <v>465</v>
       </c>
-      <c r="D130" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E130" s="2" t="s">
+      <c r="D130" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F130" t="s">
@@ -6408,10 +5710,10 @@
       <c r="C131" t="s">
         <v>465</v>
       </c>
-      <c r="D131" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E131" s="2" t="s">
+      <c r="D131" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F131" t="s">
@@ -6438,10 +5740,10 @@
       <c r="C132" t="s">
         <v>465</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E132" s="2" t="s">
+      <c r="D132" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E132" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F132" t="s">
@@ -6468,10 +5770,10 @@
       <c r="C133" t="s">
         <v>465</v>
       </c>
-      <c r="D133" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E133" s="2" t="s">
+      <c r="D133" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F133" t="s">
@@ -6498,10 +5800,10 @@
       <c r="C134" t="s">
         <v>465</v>
       </c>
-      <c r="D134" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E134" s="2" t="s">
+      <c r="D134" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F134" t="s">
@@ -6528,10 +5830,10 @@
       <c r="C135" t="s">
         <v>465</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E135" s="2" t="s">
+      <c r="D135" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F135" t="s">
@@ -6558,10 +5860,10 @@
       <c r="C136" t="s">
         <v>465</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E136" s="2" t="s">
+      <c r="D136" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F136" t="s">
@@ -6588,10 +5890,10 @@
       <c r="C137" t="s">
         <v>465</v>
       </c>
-      <c r="D137" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E137" s="2" t="s">
+      <c r="D137" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F137" t="s">
@@ -6618,10 +5920,10 @@
       <c r="C138" t="s">
         <v>465</v>
       </c>
-      <c r="D138" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E138" s="2" t="s">
+      <c r="D138" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F138" t="s">
@@ -6648,10 +5950,10 @@
       <c r="C139" t="s">
         <v>465</v>
       </c>
-      <c r="D139" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E139" s="2" t="s">
+      <c r="D139" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E139" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F139" t="s">
@@ -6678,10 +5980,10 @@
       <c r="C140" t="s">
         <v>465</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E140" s="2" t="s">
+      <c r="D140" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F140" t="s">
@@ -6708,10 +6010,10 @@
       <c r="C141" t="s">
         <v>465</v>
       </c>
-      <c r="D141" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E141" s="2" t="s">
+      <c r="D141" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F141" t="s">
@@ -6738,10 +6040,10 @@
       <c r="C142" t="s">
         <v>465</v>
       </c>
-      <c r="D142" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E142" s="2" t="s">
+      <c r="D142" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F142" t="s">
@@ -6768,10 +6070,10 @@
       <c r="C143" t="s">
         <v>465</v>
       </c>
-      <c r="D143" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E143" s="2" t="s">
+      <c r="D143" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F143" t="s">
@@ -6798,10 +6100,10 @@
       <c r="C144" t="s">
         <v>465</v>
       </c>
-      <c r="D144" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E144" s="2" t="s">
+      <c r="D144" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F144" t="s">
@@ -6828,10 +6130,10 @@
       <c r="C145" t="s">
         <v>465</v>
       </c>
-      <c r="D145" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E145" s="2" t="s">
+      <c r="D145" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E145" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F145" t="s">
@@ -6858,10 +6160,10 @@
       <c r="C146" t="s">
         <v>465</v>
       </c>
-      <c r="D146" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E146" s="2" t="s">
+      <c r="D146" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F146" t="s">
@@ -6888,10 +6190,10 @@
       <c r="C147" t="s">
         <v>465</v>
       </c>
-      <c r="D147" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E147" s="2" t="s">
+      <c r="D147" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F147" t="s">
@@ -6918,10 +6220,10 @@
       <c r="C148" t="s">
         <v>465</v>
       </c>
-      <c r="D148" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E148" s="2" t="s">
+      <c r="D148" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F148" t="s">
@@ -6948,10 +6250,10 @@
       <c r="C149" t="s">
         <v>465</v>
       </c>
-      <c r="D149" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E149" s="2" t="s">
+      <c r="D149" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F149" t="s">
@@ -6978,10 +6280,10 @@
       <c r="C150" t="s">
         <v>465</v>
       </c>
-      <c r="D150" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E150" s="2" t="s">
+      <c r="D150" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F150" t="s">
@@ -7008,10 +6310,10 @@
       <c r="C151" t="s">
         <v>465</v>
       </c>
-      <c r="D151" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E151" s="2" t="s">
+      <c r="D151" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F151" t="s">
@@ -7038,10 +6340,10 @@
       <c r="C152" t="s">
         <v>465</v>
       </c>
-      <c r="D152" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E152" s="2" t="s">
+      <c r="D152" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F152" t="s">
@@ -7068,10 +6370,10 @@
       <c r="C153" t="s">
         <v>465</v>
       </c>
-      <c r="D153" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E153" s="2" t="s">
+      <c r="D153" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F153" t="s">
@@ -7098,10 +6400,10 @@
       <c r="C154" t="s">
         <v>465</v>
       </c>
-      <c r="D154" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E154" s="2" t="s">
+      <c r="D154" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F154" t="s">
@@ -7128,10 +6430,10 @@
       <c r="C155" t="s">
         <v>465</v>
       </c>
-      <c r="D155" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E155" s="2" t="s">
+      <c r="D155" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F155" t="s">
@@ -7158,10 +6460,10 @@
       <c r="C156" t="s">
         <v>465</v>
       </c>
-      <c r="D156" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E156" s="2" t="s">
+      <c r="D156" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E156" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F156" t="s">
@@ -7188,10 +6490,10 @@
       <c r="C157" t="s">
         <v>465</v>
       </c>
-      <c r="D157" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E157" s="2" t="s">
+      <c r="D157" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F157" t="s">
@@ -7218,10 +6520,10 @@
       <c r="C158" t="s">
         <v>465</v>
       </c>
-      <c r="D158" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E158" s="2" t="s">
+      <c r="D158" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F158" t="s">
@@ -7248,10 +6550,10 @@
       <c r="C159" t="s">
         <v>465</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E159" s="2" t="s">
+      <c r="D159" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F159" t="s">
@@ -7278,10 +6580,10 @@
       <c r="C160" t="s">
         <v>465</v>
       </c>
-      <c r="D160" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E160" s="2" t="s">
+      <c r="D160" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F160" t="s">
@@ -7308,10 +6610,10 @@
       <c r="C161" t="s">
         <v>465</v>
       </c>
-      <c r="D161" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E161" s="2" t="s">
+      <c r="D161" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E161" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F161" t="s">
@@ -7338,10 +6640,10 @@
       <c r="C162" t="s">
         <v>465</v>
       </c>
-      <c r="D162" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E162" s="2" t="s">
+      <c r="D162" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F162" t="s">
@@ -7368,10 +6670,10 @@
       <c r="C163" t="s">
         <v>465</v>
       </c>
-      <c r="D163" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E163" s="2" t="s">
+      <c r="D163" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F163" t="s">
@@ -7398,10 +6700,10 @@
       <c r="C164" t="s">
         <v>465</v>
       </c>
-      <c r="D164" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E164" s="2" t="s">
+      <c r="D164" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F164" t="s">
@@ -7428,10 +6730,10 @@
       <c r="C165" t="s">
         <v>465</v>
       </c>
-      <c r="D165" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E165" s="2" t="s">
+      <c r="D165" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F165" t="s">
@@ -7458,10 +6760,10 @@
       <c r="C166" t="s">
         <v>465</v>
       </c>
-      <c r="D166" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E166" s="2" t="s">
+      <c r="D166" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F166" t="s">
@@ -7488,10 +6790,10 @@
       <c r="C167" t="s">
         <v>465</v>
       </c>
-      <c r="D167" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E167" s="2" t="s">
+      <c r="D167" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E167" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F167" t="s">
@@ -7518,10 +6820,10 @@
       <c r="C168" t="s">
         <v>465</v>
       </c>
-      <c r="D168" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E168" s="2" t="s">
+      <c r="D168" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E168" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F168" t="s">
@@ -7548,10 +6850,10 @@
       <c r="C169" t="s">
         <v>465</v>
       </c>
-      <c r="D169" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E169" s="2" t="s">
+      <c r="D169" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E169" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F169" t="s">
@@ -7578,10 +6880,10 @@
       <c r="C170" t="s">
         <v>465</v>
       </c>
-      <c r="D170" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E170" s="2" t="s">
+      <c r="D170" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E170" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F170" t="s">
@@ -7608,10 +6910,10 @@
       <c r="C171" t="s">
         <v>465</v>
       </c>
-      <c r="D171" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E171" s="2" t="s">
+      <c r="D171" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E171" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F171" t="s">
@@ -7638,10 +6940,10 @@
       <c r="C172" t="s">
         <v>465</v>
       </c>
-      <c r="D172" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E172" s="2" t="s">
+      <c r="D172" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F172" t="s">
@@ -7668,10 +6970,10 @@
       <c r="C173" t="s">
         <v>465</v>
       </c>
-      <c r="D173" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E173" s="2" t="s">
+      <c r="D173" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F173" t="s">
@@ -7698,10 +7000,10 @@
       <c r="C174" t="s">
         <v>465</v>
       </c>
-      <c r="D174" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E174" s="2" t="s">
+      <c r="D174" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F174" t="s">
@@ -7728,10 +7030,10 @@
       <c r="C175" t="s">
         <v>465</v>
       </c>
-      <c r="D175" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E175" s="2" t="s">
+      <c r="D175" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F175" t="s">
@@ -7758,10 +7060,10 @@
       <c r="C176" t="s">
         <v>465</v>
       </c>
-      <c r="D176" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E176" s="2" t="s">
+      <c r="D176" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E176" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F176" t="s">
@@ -7788,10 +7090,10 @@
       <c r="C177" t="s">
         <v>465</v>
       </c>
-      <c r="D177" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E177" s="2" t="s">
+      <c r="D177" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E177" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F177" t="s">
@@ -7818,10 +7120,10 @@
       <c r="C178" t="s">
         <v>465</v>
       </c>
-      <c r="D178" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E178" s="2" t="s">
+      <c r="D178" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F178" t="s">
@@ -7848,10 +7150,10 @@
       <c r="C179" t="s">
         <v>465</v>
       </c>
-      <c r="D179" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E179" s="2" t="s">
+      <c r="D179" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E179" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F179" t="s">
@@ -7878,10 +7180,10 @@
       <c r="C180" t="s">
         <v>465</v>
       </c>
-      <c r="D180" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E180" s="2" t="s">
+      <c r="D180" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F180" t="s">
@@ -7908,10 +7210,10 @@
       <c r="C181" t="s">
         <v>465</v>
       </c>
-      <c r="D181" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E181" s="2" t="s">
+      <c r="D181" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F181" t="s">
@@ -7938,10 +7240,10 @@
       <c r="C182" t="s">
         <v>465</v>
       </c>
-      <c r="D182" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E182" s="2" t="s">
+      <c r="D182" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F182" t="s">
@@ -7968,10 +7270,10 @@
       <c r="C183" t="s">
         <v>465</v>
       </c>
-      <c r="D183" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E183" s="2" t="s">
+      <c r="D183" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F183" t="s">
@@ -7998,10 +7300,10 @@
       <c r="C184" t="s">
         <v>465</v>
       </c>
-      <c r="D184" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E184" s="2" t="s">
+      <c r="D184" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F184" t="s">
@@ -8028,10 +7330,10 @@
       <c r="C185" t="s">
         <v>465</v>
       </c>
-      <c r="D185" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E185" s="2" t="s">
+      <c r="D185" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F185" t="s">
@@ -8058,10 +7360,10 @@
       <c r="C186" t="s">
         <v>465</v>
       </c>
-      <c r="D186" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E186" s="2" t="s">
+      <c r="D186" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F186" t="s">
@@ -8088,10 +7390,10 @@
       <c r="C187" t="s">
         <v>465</v>
       </c>
-      <c r="D187" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E187" s="2" t="s">
+      <c r="D187" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F187" t="s">
@@ -8118,10 +7420,10 @@
       <c r="C188" t="s">
         <v>465</v>
       </c>
-      <c r="D188" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E188" s="2" t="s">
+      <c r="D188" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E188" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F188" t="s">
@@ -8148,10 +7450,10 @@
       <c r="C189" t="s">
         <v>465</v>
       </c>
-      <c r="D189" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E189" s="2" t="s">
+      <c r="D189" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F189" t="s">
@@ -8178,10 +7480,10 @@
       <c r="C190" t="s">
         <v>465</v>
       </c>
-      <c r="D190" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E190" s="2" t="s">
+      <c r="D190" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F190" t="s">
@@ -8208,10 +7510,10 @@
       <c r="C191" t="s">
         <v>465</v>
       </c>
-      <c r="D191" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E191" s="2" t="s">
+      <c r="D191" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E191" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F191" t="s">
@@ -8238,10 +7540,10 @@
       <c r="C192" t="s">
         <v>465</v>
       </c>
-      <c r="D192" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E192" s="2" t="s">
+      <c r="D192" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F192" t="s">
@@ -8268,10 +7570,10 @@
       <c r="C193" t="s">
         <v>465</v>
       </c>
-      <c r="D193" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E193" s="2" t="s">
+      <c r="D193" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F193" t="s">
@@ -8298,10 +7600,10 @@
       <c r="C194" t="s">
         <v>465</v>
       </c>
-      <c r="D194" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E194" s="2" t="s">
+      <c r="D194" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F194" t="s">
@@ -8328,10 +7630,10 @@
       <c r="C195" t="s">
         <v>465</v>
       </c>
-      <c r="D195" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E195" s="2" t="s">
+      <c r="D195" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E195" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F195" t="s">
@@ -8358,10 +7660,10 @@
       <c r="C196" t="s">
         <v>465</v>
       </c>
-      <c r="D196" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E196" s="2" t="s">
+      <c r="D196" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F196" t="s">
@@ -8388,10 +7690,10 @@
       <c r="C197" t="s">
         <v>465</v>
       </c>
-      <c r="D197" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E197" s="2" t="s">
+      <c r="D197" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F197" t="s">
@@ -8418,10 +7720,10 @@
       <c r="C198" t="s">
         <v>465</v>
       </c>
-      <c r="D198" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E198" s="2" t="s">
+      <c r="D198" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F198" t="s">
@@ -8448,10 +7750,10 @@
       <c r="C199" t="s">
         <v>465</v>
       </c>
-      <c r="D199" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E199" s="2" t="s">
+      <c r="D199" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F199" t="s">
@@ -8478,10 +7780,10 @@
       <c r="C200" t="s">
         <v>465</v>
       </c>
-      <c r="D200" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E200" s="2" t="s">
+      <c r="D200" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E200" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F200" t="s">
@@ -8508,10 +7810,10 @@
       <c r="C201" t="s">
         <v>465</v>
       </c>
-      <c r="D201" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E201" s="2" t="s">
+      <c r="D201" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F201" t="s">
@@ -8538,10 +7840,10 @@
       <c r="C202" t="s">
         <v>465</v>
       </c>
-      <c r="D202" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E202" s="2" t="s">
+      <c r="D202" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F202" t="s">
@@ -8568,10 +7870,10 @@
       <c r="C203" t="s">
         <v>465</v>
       </c>
-      <c r="D203" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E203" s="2" t="s">
+      <c r="D203" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E203" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F203" t="s">
@@ -8598,10 +7900,10 @@
       <c r="C204" t="s">
         <v>465</v>
       </c>
-      <c r="D204" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E204" s="2" t="s">
+      <c r="D204" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E204" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F204" t="s">
@@ -8628,10 +7930,10 @@
       <c r="C205" t="s">
         <v>465</v>
       </c>
-      <c r="D205" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E205" s="2" t="s">
+      <c r="D205" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F205" t="s">
@@ -8658,10 +7960,10 @@
       <c r="C206" t="s">
         <v>465</v>
       </c>
-      <c r="D206" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E206" s="2" t="s">
+      <c r="D206" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E206" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F206" t="s">
@@ -8688,10 +7990,10 @@
       <c r="C207" t="s">
         <v>465</v>
       </c>
-      <c r="D207" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E207" s="2" t="s">
+      <c r="D207" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E207" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F207" t="s">
@@ -8718,10 +8020,10 @@
       <c r="C208" t="s">
         <v>465</v>
       </c>
-      <c r="D208" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E208" s="2" t="s">
+      <c r="D208" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F208" t="s">
@@ -8748,10 +8050,10 @@
       <c r="C209" t="s">
         <v>465</v>
       </c>
-      <c r="D209" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E209" s="2" t="s">
+      <c r="D209" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E209" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F209" t="s">
@@ -8778,10 +8080,10 @@
       <c r="C210" t="s">
         <v>465</v>
       </c>
-      <c r="D210" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E210" s="2" t="s">
+      <c r="D210" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E210" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F210" t="s">
@@ -8808,10 +8110,10 @@
       <c r="C211" t="s">
         <v>465</v>
       </c>
-      <c r="D211" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E211" s="2" t="s">
+      <c r="D211" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E211" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F211" t="s">
@@ -8838,10 +8140,10 @@
       <c r="C212" t="s">
         <v>465</v>
       </c>
-      <c r="D212" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E212" s="2" t="s">
+      <c r="D212" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E212" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F212" t="s">
@@ -8868,10 +8170,10 @@
       <c r="C213" t="s">
         <v>465</v>
       </c>
-      <c r="D213" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E213" s="2" t="s">
+      <c r="D213" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E213" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F213" t="s">
@@ -8898,10 +8200,10 @@
       <c r="C214" t="s">
         <v>465</v>
       </c>
-      <c r="D214" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E214" s="2" t="s">
+      <c r="D214" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E214" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F214" t="s">
@@ -8928,10 +8230,10 @@
       <c r="C215" t="s">
         <v>465</v>
       </c>
-      <c r="D215" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E215" s="2" t="s">
+      <c r="D215" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E215" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F215" t="s">
@@ -8958,10 +8260,10 @@
       <c r="C216" t="s">
         <v>465</v>
       </c>
-      <c r="D216" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E216" s="2" t="s">
+      <c r="D216" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E216" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F216" t="s">
@@ -8988,10 +8290,10 @@
       <c r="C217" t="s">
         <v>465</v>
       </c>
-      <c r="D217" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E217" s="2" t="s">
+      <c r="D217" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E217" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F217" t="s">
@@ -9018,10 +8320,10 @@
       <c r="C218" t="s">
         <v>465</v>
       </c>
-      <c r="D218" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E218" s="2" t="s">
+      <c r="D218" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E218" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F218" t="s">
@@ -9048,10 +8350,10 @@
       <c r="C219" t="s">
         <v>465</v>
       </c>
-      <c r="D219" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E219" s="2" t="s">
+      <c r="D219" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E219" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F219" t="s">
@@ -9078,10 +8380,10 @@
       <c r="C220" t="s">
         <v>465</v>
       </c>
-      <c r="D220" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E220" s="2" t="s">
+      <c r="D220" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E220" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F220" t="s">
@@ -9108,10 +8410,10 @@
       <c r="C221" t="s">
         <v>465</v>
       </c>
-      <c r="D221" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E221" s="2" t="s">
+      <c r="D221" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E221" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F221" t="s">
@@ -9138,10 +8440,10 @@
       <c r="C222" t="s">
         <v>465</v>
       </c>
-      <c r="D222" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E222" s="2" t="s">
+      <c r="D222" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E222" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F222" t="s">
@@ -9168,10 +8470,10 @@
       <c r="C223" t="s">
         <v>465</v>
       </c>
-      <c r="D223" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E223" s="2" t="s">
+      <c r="D223" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E223" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F223" t="s">
@@ -9198,10 +8500,10 @@
       <c r="C224" t="s">
         <v>465</v>
       </c>
-      <c r="D224" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E224" s="2" t="s">
+      <c r="D224" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E224" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F224" t="s">
@@ -9228,10 +8530,10 @@
       <c r="C225" t="s">
         <v>465</v>
       </c>
-      <c r="D225" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E225" s="2" t="s">
+      <c r="D225" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E225" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F225" t="s">
@@ -9258,10 +8560,10 @@
       <c r="C226" t="s">
         <v>465</v>
       </c>
-      <c r="D226" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E226" s="2" t="s">
+      <c r="D226" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E226" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F226" t="s">
@@ -9288,10 +8590,10 @@
       <c r="C227" t="s">
         <v>465</v>
       </c>
-      <c r="D227" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E227" s="2" t="s">
+      <c r="D227" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E227" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F227" t="s">
@@ -9318,10 +8620,10 @@
       <c r="C228" t="s">
         <v>465</v>
       </c>
-      <c r="D228" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E228" s="2" t="s">
+      <c r="D228" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E228" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F228" t="s">
@@ -9348,10 +8650,10 @@
       <c r="C229" t="s">
         <v>465</v>
       </c>
-      <c r="D229" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E229" s="2" t="s">
+      <c r="D229" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E229" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F229" t="s">
@@ -9378,10 +8680,10 @@
       <c r="C230" t="s">
         <v>465</v>
       </c>
-      <c r="D230" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E230" s="2" t="s">
+      <c r="D230" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E230" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F230" t="s">
@@ -9408,10 +8710,10 @@
       <c r="C231" t="s">
         <v>465</v>
       </c>
-      <c r="D231" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E231" s="2" t="s">
+      <c r="D231" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E231" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F231" t="s">
@@ -9438,10 +8740,10 @@
       <c r="C232" t="s">
         <v>465</v>
       </c>
-      <c r="D232" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E232" s="2" t="s">
+      <c r="D232" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E232" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F232" t="s">
@@ -9468,10 +8770,10 @@
       <c r="C233" t="s">
         <v>465</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E233" s="2" t="s">
+      <c r="D233" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E233" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F233" t="s">
@@ -9498,10 +8800,10 @@
       <c r="C234" t="s">
         <v>465</v>
       </c>
-      <c r="D234" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E234" s="2" t="s">
+      <c r="D234" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E234" s="1" t="s">
         <v>461</v>
       </c>
       <c r="F234" t="s">
@@ -9522,1187 +8824,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5513FBAC-96E4-4BDF-A6C6-DF5DEEA053B5}">
-  <dimension ref="A1:A234"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="1" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="1" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="1" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="1" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="1" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="1" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="1" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="1" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="1" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="1" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="1" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="1" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="1" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="1" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="1" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="1" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="1" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="1" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="1" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="1" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="1" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="1" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="1" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="1" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" s="1" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" s="1" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200" s="1" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" s="1" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A202" s="1" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A203" s="1" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A204" s="1" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205" s="1" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A206" s="1" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A207" s="1" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A208" s="1" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A209" s="1" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A210" s="1" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A211" s="1" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A212" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A213" s="1" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A214" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A215" s="1" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A216" s="1" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A217" s="1" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A218" s="1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A219" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A223" s="1" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A224" s="1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A225" s="1" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A226" s="1" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227" s="1" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A228" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A229" s="1" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A230" s="1" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A231" s="1" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
-        <v>695</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/ussd-api-master/Documentations/countryList.xlsx
+++ b/ussd-api-master/Documentations/countryList.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspaces\workspace1\ussd-api-master\ussd-api-master\Documentations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eclipse-workspace\workspace1\ussd-api-master\Documentations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641207C1-2CCA-4083-9B50-313622801D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3659866-0939-4A21-A0A2-D27D4F629B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{47B715E9-E7F4-41FB-8459-15FB7DB0CB70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{47B715E9-E7F4-41FB-8459-15FB7DB0CB70}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="696">
   <si>
     <t>United States</t>
   </si>
@@ -1434,19 +1435,715 @@
   </si>
   <si>
     <t xml:space="preserve"> WHERE NOT EXISTS ( SELECT 1 FROM country WHERE  country_code =  </t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','United States','US');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','United Kingdom','GB');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Canada','CA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Australia','AU');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Afghanistan','AF');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Albania','AL');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Algeria','DZ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','American Samoa','AS');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Andorra','AD');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Angola','AO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Anguilla','AI');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Antarctica','AQ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Antigua and Barbuda ','AG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Argentina','AR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Armenia','AM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Aruba','AW');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Austria','AT');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Azerbaijan','AZ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Bahamas','BS');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Bahrain','BH');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Bangladesh','BD');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Barbados','BB');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Belarus','BY');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Belgium','BE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Belize','BZ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Benin','BJ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Bermuda','BM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Bhutan','BT');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Bolivia','BO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Bosnia and Herzegovina','BA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Botswana','BW');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Brazil','BR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','British Indian Ocean','IO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Brunei','BN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Bulgaria','BG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Burkina Faso','BF');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Burma (Myanmar)','MM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Burundi','BI');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Cambodia','KH');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Cameroon','CM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Cape Verde','CV');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Cayman Islands','KY');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Central African Republic','CF');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Chad','TD');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Chile','CL');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','China','CN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Christmas Island','CX');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Cocos (Keeling) Islands','CC');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Colombia','CO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Comoros','KM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Congo, Democratic Republic of the','CD');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Congo, Republic of the','CG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Cook Islands','CK');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Costa Rica','CR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Croatia','HR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Cyprus','CY');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Czech Republic','CZ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Denmark','DK');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Djibouti','DJ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Dominica','DM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Dominican Republic','DO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','East Timor','TL');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Ecuador','EC');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Egypt','EG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','El Salvador','SV');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Equatorial Guinea','GQ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Eritrea','ER');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Estonia','EE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Ethiopia','ET');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Falkland Islands (Malvinas)','FK');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Faroe Islands','FO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Fiji','FJ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Finland','FI');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','France','FR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','French Guiana','GF');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','French Polynesia','PF');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Gabon','GA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Gambia','GM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Georgia','GE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Germany','DE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Ghana','GH');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Gibraltar','GI');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Greece','GR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Greenland','GL');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Grenada','GD');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Guadeloupe','GP');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Guam','GU');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Guatemala','GT');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Guinea','GN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Guinea-Bissau','GW');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Guyana','GY');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Haiti','HT');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Honduras','HN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Hong Kong','HK');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Hungary','HU');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Iceland','IS');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','India','IN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Indonesia','ID');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Iraq','IQ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Ireland','IE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Israel','IL');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Italy','IT');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Ivory Coast','CI');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Jamaica','JM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Japan','JP');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Jordan','JO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Kazakhstan','KZ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Kenya','KE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Kiribati','KI');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Korea, South','KR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Kuwait','KW');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Kyrgyzstan','KG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Laos','LA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Latvia','LV');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Lebanon','LB');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Lesotho','LS');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Liberia','LR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Liechtenstein','LI');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Lithuania','LT');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Luxembourg','LU');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Macau','MO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Macedonia, Republic of','MK');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Madagascar','MG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Malawi','MW');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Malaysia','MY');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Maldives','MV');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Mali','ML');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Malta','MT');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Marshall Islands','MH');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Martinique','MQ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Mauritania','MR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Mauritius','MU');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Mayotte','YT');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Mexico','MX');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Micronesia','FM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Moldova','MD');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Monaco','MC');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Mongolia','MN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Montserrat','MS');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Morocco','MA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Mozambique','MZ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Namibia','NA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Nauru','NR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Nepal','NP');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Netherlands','NL');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Netherlands Antilles','AN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','New Caledonia','NC');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','New Zealand','NZ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Nicaragua','NI');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Niger','NE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Nigeria','NG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Niue','NU');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Norfolk Island','NF');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Northern Mariana Islands','MP');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Norway','NO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Oman','OM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Pakistan','PK');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Palau','PW');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Palestinian Territory','PS');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Panama','PA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Papua New Guinea','PG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Paraguay','PY');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Peru','PE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Philippines','PH');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Pitcairn Island','PN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Poland','PL');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Portugal','PT');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Puerto Rico','PR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Qatar','QA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Reunion','RE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Romania','RO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Russia','RU');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Rwanda','RW');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Saint Helena','SH');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Saint Kitts and Nevis','KN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Saint Lucia','LC');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Saint Pierre and Miquelon','PM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Saint Vincent and the Grenadines','VC');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Samoa','WS');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','San Marino','SM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Sao Tome and Principe','ST');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Saudi Arabia','SA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Senegal','SN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Serbia and Montenegro','CS');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Seychelles','SC');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Sierra Leone','SL');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Singapore','SG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Slovakia','SK');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Slovenia','SI');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Solomon Islands','SB');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Somalia','SO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','South Africa','ZA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','South Georgia and the South Sandwich Islands','GS');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Spain','ES');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Sri Lanka','LK');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Suriname','SR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Svalbard and Jan Mayen','SJ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Swaziland','SZ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Sweden','SE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Switzerland','CH');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Taiwan','TW');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Tajikistan','TJ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Tanzania','TZ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Thailand','TH');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Togo','TG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Tokelau','TK');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Tonga','TO');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Trinidad and Tobago','TT');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Tunisia','TN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Turkey','TR');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Turkmenistan','TM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Turks and Caicos Islands','TC');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Tuvalu','TV');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Uganda','UG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Ukraine','UA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','United Arab Emirates','AE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','United States Minor Outlying Islands','UM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Uruguay','UY');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Uzbekistan','UZ');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Vanuatu','VU');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Vatican City','VA');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Venezuela','VE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Vietnam','VN');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Virgin Islands, British','VG');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Virgin Islands, U. S.','VI');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Wallis and Futuna','WF');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Western Sahara','EH');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Yemen','YE');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Zambia','ZM');</t>
+  </si>
+  <si>
+    <t>INSERT INTO country values('','Zimbabw','ZW');</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1469,8 +2166,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1795,8 +2495,6 @@
     <col min="4" max="5" width="5.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" customWidth="1"/>
     <col min="7" max="7" width="25.5703125" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="57.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1810,10 +2508,10 @@
       <c r="C1" t="s">
         <v>465</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F1" t="s">
@@ -1840,10 +2538,10 @@
       <c r="C2" t="s">
         <v>465</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F2" t="s">
@@ -1870,10 +2568,10 @@
       <c r="C3" t="s">
         <v>465</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F3" t="s">
@@ -1900,10 +2598,10 @@
       <c r="C4" t="s">
         <v>465</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F4" t="s">
@@ -1930,10 +2628,10 @@
       <c r="C5" t="s">
         <v>465</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F5" t="s">
@@ -1960,10 +2658,10 @@
       <c r="C6" t="s">
         <v>465</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F6" t="s">
@@ -1990,10 +2688,10 @@
       <c r="C7" t="s">
         <v>465</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F7" t="s">
@@ -2020,10 +2718,10 @@
       <c r="C8" t="s">
         <v>465</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F8" t="s">
@@ -2050,10 +2748,10 @@
       <c r="C9" t="s">
         <v>465</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F9" t="s">
@@ -2080,10 +2778,10 @@
       <c r="C10" t="s">
         <v>465</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D10" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F10" t="s">
@@ -2110,10 +2808,10 @@
       <c r="C11" t="s">
         <v>465</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F11" t="s">
@@ -2140,10 +2838,10 @@
       <c r="C12" t="s">
         <v>465</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F12" t="s">
@@ -2170,10 +2868,10 @@
       <c r="C13" t="s">
         <v>465</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F13" t="s">
@@ -2200,10 +2898,10 @@
       <c r="C14" t="s">
         <v>465</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F14" t="s">
@@ -2230,10 +2928,10 @@
       <c r="C15" t="s">
         <v>465</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="D15" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F15" t="s">
@@ -2260,10 +2958,10 @@
       <c r="C16" t="s">
         <v>465</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F16" t="s">
@@ -2290,10 +2988,10 @@
       <c r="C17" t="s">
         <v>465</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="D17" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F17" t="s">
@@ -2320,10 +3018,10 @@
       <c r="C18" t="s">
         <v>465</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="D18" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F18" t="s">
@@ -2350,10 +3048,10 @@
       <c r="C19" t="s">
         <v>465</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="D19" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F19" t="s">
@@ -2380,10 +3078,10 @@
       <c r="C20" t="s">
         <v>465</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="D20" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F20" t="s">
@@ -2410,10 +3108,10 @@
       <c r="C21" t="s">
         <v>465</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="D21" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F21" t="s">
@@ -2440,10 +3138,10 @@
       <c r="C22" t="s">
         <v>465</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="D22" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F22" t="s">
@@ -2470,10 +3168,10 @@
       <c r="C23" t="s">
         <v>465</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="D23" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F23" t="s">
@@ -2500,10 +3198,10 @@
       <c r="C24" t="s">
         <v>465</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="D24" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F24" t="s">
@@ -2530,10 +3228,10 @@
       <c r="C25" t="s">
         <v>465</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="D25" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F25" t="s">
@@ -2560,10 +3258,10 @@
       <c r="C26" t="s">
         <v>465</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="D26" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F26" t="s">
@@ -2590,10 +3288,10 @@
       <c r="C27" t="s">
         <v>465</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="D27" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F27" t="s">
@@ -2620,10 +3318,10 @@
       <c r="C28" t="s">
         <v>465</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="D28" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F28" t="s">
@@ -2650,10 +3348,10 @@
       <c r="C29" t="s">
         <v>465</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="D29" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F29" t="s">
@@ -2680,10 +3378,10 @@
       <c r="C30" t="s">
         <v>465</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="D30" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F30" t="s">
@@ -2710,10 +3408,10 @@
       <c r="C31" t="s">
         <v>465</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="D31" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F31" t="s">
@@ -2740,10 +3438,10 @@
       <c r="C32" t="s">
         <v>465</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E32" s="1" t="s">
+      <c r="D32" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F32" t="s">
@@ -2770,10 +3468,10 @@
       <c r="C33" t="s">
         <v>465</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="D33" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F33" t="s">
@@ -2800,10 +3498,10 @@
       <c r="C34" t="s">
         <v>465</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="D34" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F34" t="s">
@@ -2830,10 +3528,10 @@
       <c r="C35" t="s">
         <v>465</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="D35" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F35" t="s">
@@ -2860,10 +3558,10 @@
       <c r="C36" t="s">
         <v>465</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="D36" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F36" t="s">
@@ -2890,10 +3588,10 @@
       <c r="C37" t="s">
         <v>465</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="D37" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F37" t="s">
@@ -2920,10 +3618,10 @@
       <c r="C38" t="s">
         <v>465</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="D38" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F38" t="s">
@@ -2950,10 +3648,10 @@
       <c r="C39" t="s">
         <v>465</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="D39" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F39" t="s">
@@ -2980,10 +3678,10 @@
       <c r="C40" t="s">
         <v>465</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="D40" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F40" t="s">
@@ -3010,10 +3708,10 @@
       <c r="C41" t="s">
         <v>465</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="D41" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F41" t="s">
@@ -3040,10 +3738,10 @@
       <c r="C42" t="s">
         <v>465</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="D42" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F42" t="s">
@@ -3070,10 +3768,10 @@
       <c r="C43" t="s">
         <v>465</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="D43" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F43" t="s">
@@ -3100,10 +3798,10 @@
       <c r="C44" t="s">
         <v>465</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="D44" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F44" t="s">
@@ -3130,10 +3828,10 @@
       <c r="C45" t="s">
         <v>465</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="D45" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F45" t="s">
@@ -3160,10 +3858,10 @@
       <c r="C46" t="s">
         <v>465</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="D46" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F46" t="s">
@@ -3190,10 +3888,10 @@
       <c r="C47" t="s">
         <v>465</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="D47" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F47" t="s">
@@ -3220,10 +3918,10 @@
       <c r="C48" t="s">
         <v>465</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E48" s="1" t="s">
+      <c r="D48" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F48" t="s">
@@ -3250,10 +3948,10 @@
       <c r="C49" t="s">
         <v>465</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="D49" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F49" t="s">
@@ -3280,10 +3978,10 @@
       <c r="C50" t="s">
         <v>465</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E50" s="1" t="s">
+      <c r="D50" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F50" t="s">
@@ -3310,10 +4008,10 @@
       <c r="C51" t="s">
         <v>465</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E51" s="1" t="s">
+      <c r="D51" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F51" t="s">
@@ -3340,10 +4038,10 @@
       <c r="C52" t="s">
         <v>465</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="D52" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F52" t="s">
@@ -3370,10 +4068,10 @@
       <c r="C53" t="s">
         <v>465</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E53" s="1" t="s">
+      <c r="D53" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F53" t="s">
@@ -3400,10 +4098,10 @@
       <c r="C54" t="s">
         <v>465</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E54" s="1" t="s">
+      <c r="D54" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F54" t="s">
@@ -3430,10 +4128,10 @@
       <c r="C55" t="s">
         <v>465</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="D55" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F55" t="s">
@@ -3460,10 +4158,10 @@
       <c r="C56" t="s">
         <v>465</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="D56" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F56" t="s">
@@ -3490,10 +4188,10 @@
       <c r="C57" t="s">
         <v>465</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="D57" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F57" t="s">
@@ -3520,10 +4218,10 @@
       <c r="C58" t="s">
         <v>465</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="D58" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F58" t="s">
@@ -3550,10 +4248,10 @@
       <c r="C59" t="s">
         <v>465</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="D59" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F59" t="s">
@@ -3580,10 +4278,10 @@
       <c r="C60" t="s">
         <v>465</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="D60" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F60" t="s">
@@ -3610,10 +4308,10 @@
       <c r="C61" t="s">
         <v>465</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="D61" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F61" t="s">
@@ -3640,10 +4338,10 @@
       <c r="C62" t="s">
         <v>465</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E62" s="1" t="s">
+      <c r="D62" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F62" t="s">
@@ -3670,10 +4368,10 @@
       <c r="C63" t="s">
         <v>465</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E63" s="1" t="s">
+      <c r="D63" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F63" t="s">
@@ -3700,10 +4398,10 @@
       <c r="C64" t="s">
         <v>465</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E64" s="1" t="s">
+      <c r="D64" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F64" t="s">
@@ -3730,10 +4428,10 @@
       <c r="C65" t="s">
         <v>465</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E65" s="1" t="s">
+      <c r="D65" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F65" t="s">
@@ -3760,10 +4458,10 @@
       <c r="C66" t="s">
         <v>465</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E66" s="1" t="s">
+      <c r="D66" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F66" t="s">
@@ -3790,10 +4488,10 @@
       <c r="C67" t="s">
         <v>465</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="D67" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F67" t="s">
@@ -3820,10 +4518,10 @@
       <c r="C68" t="s">
         <v>465</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E68" s="1" t="s">
+      <c r="D68" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F68" t="s">
@@ -3850,10 +4548,10 @@
       <c r="C69" t="s">
         <v>465</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E69" s="1" t="s">
+      <c r="D69" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F69" t="s">
@@ -3880,10 +4578,10 @@
       <c r="C70" t="s">
         <v>465</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E70" s="1" t="s">
+      <c r="D70" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F70" t="s">
@@ -3910,10 +4608,10 @@
       <c r="C71" t="s">
         <v>465</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E71" s="1" t="s">
+      <c r="D71" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F71" t="s">
@@ -3940,10 +4638,10 @@
       <c r="C72" t="s">
         <v>465</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E72" s="1" t="s">
+      <c r="D72" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F72" t="s">
@@ -3970,10 +4668,10 @@
       <c r="C73" t="s">
         <v>465</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E73" s="1" t="s">
+      <c r="D73" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F73" t="s">
@@ -4000,10 +4698,10 @@
       <c r="C74" t="s">
         <v>465</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E74" s="1" t="s">
+      <c r="D74" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F74" t="s">
@@ -4030,10 +4728,10 @@
       <c r="C75" t="s">
         <v>465</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E75" s="1" t="s">
+      <c r="D75" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F75" t="s">
@@ -4060,10 +4758,10 @@
       <c r="C76" t="s">
         <v>465</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E76" s="1" t="s">
+      <c r="D76" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F76" t="s">
@@ -4090,10 +4788,10 @@
       <c r="C77" t="s">
         <v>465</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E77" s="1" t="s">
+      <c r="D77" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F77" t="s">
@@ -4120,10 +4818,10 @@
       <c r="C78" t="s">
         <v>465</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E78" s="1" t="s">
+      <c r="D78" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F78" t="s">
@@ -4150,10 +4848,10 @@
       <c r="C79" t="s">
         <v>465</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E79" s="1" t="s">
+      <c r="D79" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F79" t="s">
@@ -4180,10 +4878,10 @@
       <c r="C80" t="s">
         <v>465</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E80" s="1" t="s">
+      <c r="D80" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F80" t="s">
@@ -4210,10 +4908,10 @@
       <c r="C81" t="s">
         <v>465</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="D81" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F81" t="s">
@@ -4240,10 +4938,10 @@
       <c r="C82" t="s">
         <v>465</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E82" s="1" t="s">
+      <c r="D82" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F82" t="s">
@@ -4270,10 +4968,10 @@
       <c r="C83" t="s">
         <v>465</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E83" s="1" t="s">
+      <c r="D83" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F83" t="s">
@@ -4300,10 +4998,10 @@
       <c r="C84" t="s">
         <v>465</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="D84" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F84" t="s">
@@ -4330,10 +5028,10 @@
       <c r="C85" t="s">
         <v>465</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E85" s="1" t="s">
+      <c r="D85" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F85" t="s">
@@ -4360,10 +5058,10 @@
       <c r="C86" t="s">
         <v>465</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E86" s="1" t="s">
+      <c r="D86" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F86" t="s">
@@ -4390,10 +5088,10 @@
       <c r="C87" t="s">
         <v>465</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E87" s="1" t="s">
+      <c r="D87" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F87" t="s">
@@ -4420,10 +5118,10 @@
       <c r="C88" t="s">
         <v>465</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E88" s="1" t="s">
+      <c r="D88" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F88" t="s">
@@ -4450,10 +5148,10 @@
       <c r="C89" t="s">
         <v>465</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E89" s="1" t="s">
+      <c r="D89" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F89" t="s">
@@ -4480,10 +5178,10 @@
       <c r="C90" t="s">
         <v>465</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E90" s="1" t="s">
+      <c r="D90" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F90" t="s">
@@ -4510,10 +5208,10 @@
       <c r="C91" t="s">
         <v>465</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E91" s="1" t="s">
+      <c r="D91" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F91" t="s">
@@ -4540,10 +5238,10 @@
       <c r="C92" t="s">
         <v>465</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E92" s="1" t="s">
+      <c r="D92" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F92" t="s">
@@ -4570,10 +5268,10 @@
       <c r="C93" t="s">
         <v>465</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E93" s="1" t="s">
+      <c r="D93" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F93" t="s">
@@ -4600,10 +5298,10 @@
       <c r="C94" t="s">
         <v>465</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E94" s="1" t="s">
+      <c r="D94" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F94" t="s">
@@ -4630,10 +5328,10 @@
       <c r="C95" t="s">
         <v>465</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E95" s="1" t="s">
+      <c r="D95" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F95" t="s">
@@ -4660,10 +5358,10 @@
       <c r="C96" t="s">
         <v>465</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E96" s="1" t="s">
+      <c r="D96" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F96" t="s">
@@ -4690,10 +5388,10 @@
       <c r="C97" t="s">
         <v>465</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E97" s="1" t="s">
+      <c r="D97" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F97" t="s">
@@ -4720,10 +5418,10 @@
       <c r="C98" t="s">
         <v>465</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E98" s="1" t="s">
+      <c r="D98" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F98" t="s">
@@ -4750,10 +5448,10 @@
       <c r="C99" t="s">
         <v>465</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E99" s="1" t="s">
+      <c r="D99" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F99" t="s">
@@ -4780,10 +5478,10 @@
       <c r="C100" t="s">
         <v>465</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E100" s="1" t="s">
+      <c r="D100" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F100" t="s">
@@ -4810,10 +5508,10 @@
       <c r="C101" t="s">
         <v>465</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E101" s="1" t="s">
+      <c r="D101" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F101" t="s">
@@ -4840,10 +5538,10 @@
       <c r="C102" t="s">
         <v>465</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E102" s="1" t="s">
+      <c r="D102" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F102" t="s">
@@ -4870,10 +5568,10 @@
       <c r="C103" t="s">
         <v>465</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E103" s="1" t="s">
+      <c r="D103" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F103" t="s">
@@ -4900,10 +5598,10 @@
       <c r="C104" t="s">
         <v>465</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="D104" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F104" t="s">
@@ -4930,10 +5628,10 @@
       <c r="C105" t="s">
         <v>465</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E105" s="1" t="s">
+      <c r="D105" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F105" t="s">
@@ -4960,10 +5658,10 @@
       <c r="C106" t="s">
         <v>465</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E106" s="1" t="s">
+      <c r="D106" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F106" t="s">
@@ -4990,10 +5688,10 @@
       <c r="C107" t="s">
         <v>465</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E107" s="1" t="s">
+      <c r="D107" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F107" t="s">
@@ -5020,10 +5718,10 @@
       <c r="C108" t="s">
         <v>465</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E108" s="1" t="s">
+      <c r="D108" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F108" t="s">
@@ -5050,10 +5748,10 @@
       <c r="C109" t="s">
         <v>465</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E109" s="1" t="s">
+      <c r="D109" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F109" t="s">
@@ -5080,10 +5778,10 @@
       <c r="C110" t="s">
         <v>465</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E110" s="1" t="s">
+      <c r="D110" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F110" t="s">
@@ -5110,10 +5808,10 @@
       <c r="C111" t="s">
         <v>465</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E111" s="1" t="s">
+      <c r="D111" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F111" t="s">
@@ -5140,10 +5838,10 @@
       <c r="C112" t="s">
         <v>465</v>
       </c>
-      <c r="D112" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E112" s="1" t="s">
+      <c r="D112" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F112" t="s">
@@ -5170,10 +5868,10 @@
       <c r="C113" t="s">
         <v>465</v>
       </c>
-      <c r="D113" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E113" s="1" t="s">
+      <c r="D113" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F113" t="s">
@@ -5200,10 +5898,10 @@
       <c r="C114" t="s">
         <v>465</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E114" s="1" t="s">
+      <c r="D114" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F114" t="s">
@@ -5230,10 +5928,10 @@
       <c r="C115" t="s">
         <v>465</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E115" s="1" t="s">
+      <c r="D115" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F115" t="s">
@@ -5260,10 +5958,10 @@
       <c r="C116" t="s">
         <v>465</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E116" s="1" t="s">
+      <c r="D116" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F116" t="s">
@@ -5290,10 +5988,10 @@
       <c r="C117" t="s">
         <v>465</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E117" s="1" t="s">
+      <c r="D117" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F117" t="s">
@@ -5320,10 +6018,10 @@
       <c r="C118" t="s">
         <v>465</v>
       </c>
-      <c r="D118" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E118" s="1" t="s">
+      <c r="D118" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F118" t="s">
@@ -5350,10 +6048,10 @@
       <c r="C119" t="s">
         <v>465</v>
       </c>
-      <c r="D119" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E119" s="1" t="s">
+      <c r="D119" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F119" t="s">
@@ -5380,10 +6078,10 @@
       <c r="C120" t="s">
         <v>465</v>
       </c>
-      <c r="D120" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E120" s="1" t="s">
+      <c r="D120" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F120" t="s">
@@ -5410,10 +6108,10 @@
       <c r="C121" t="s">
         <v>465</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E121" s="1" t="s">
+      <c r="D121" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F121" t="s">
@@ -5440,10 +6138,10 @@
       <c r="C122" t="s">
         <v>465</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E122" s="1" t="s">
+      <c r="D122" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F122" t="s">
@@ -5470,10 +6168,10 @@
       <c r="C123" t="s">
         <v>465</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E123" s="1" t="s">
+      <c r="D123" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F123" t="s">
@@ -5500,10 +6198,10 @@
       <c r="C124" t="s">
         <v>465</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E124" s="1" t="s">
+      <c r="D124" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F124" t="s">
@@ -5530,10 +6228,10 @@
       <c r="C125" t="s">
         <v>465</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E125" s="1" t="s">
+      <c r="D125" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F125" t="s">
@@ -5560,10 +6258,10 @@
       <c r="C126" t="s">
         <v>465</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E126" s="1" t="s">
+      <c r="D126" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F126" t="s">
@@ -5590,10 +6288,10 @@
       <c r="C127" t="s">
         <v>465</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E127" s="1" t="s">
+      <c r="D127" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F127" t="s">
@@ -5620,10 +6318,10 @@
       <c r="C128" t="s">
         <v>465</v>
       </c>
-      <c r="D128" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E128" s="1" t="s">
+      <c r="D128" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F128" t="s">
@@ -5650,10 +6348,10 @@
       <c r="C129" t="s">
         <v>465</v>
       </c>
-      <c r="D129" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E129" s="1" t="s">
+      <c r="D129" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F129" t="s">
@@ -5680,10 +6378,10 @@
       <c r="C130" t="s">
         <v>465</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E130" s="1" t="s">
+      <c r="D130" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F130" t="s">
@@ -5710,10 +6408,10 @@
       <c r="C131" t="s">
         <v>465</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E131" s="1" t="s">
+      <c r="D131" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F131" t="s">
@@ -5740,10 +6438,10 @@
       <c r="C132" t="s">
         <v>465</v>
       </c>
-      <c r="D132" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E132" s="1" t="s">
+      <c r="D132" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F132" t="s">
@@ -5770,10 +6468,10 @@
       <c r="C133" t="s">
         <v>465</v>
       </c>
-      <c r="D133" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E133" s="1" t="s">
+      <c r="D133" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F133" t="s">
@@ -5800,10 +6498,10 @@
       <c r="C134" t="s">
         <v>465</v>
       </c>
-      <c r="D134" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E134" s="1" t="s">
+      <c r="D134" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F134" t="s">
@@ -5830,10 +6528,10 @@
       <c r="C135" t="s">
         <v>465</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E135" s="1" t="s">
+      <c r="D135" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F135" t="s">
@@ -5860,10 +6558,10 @@
       <c r="C136" t="s">
         <v>465</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E136" s="1" t="s">
+      <c r="D136" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F136" t="s">
@@ -5890,10 +6588,10 @@
       <c r="C137" t="s">
         <v>465</v>
       </c>
-      <c r="D137" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E137" s="1" t="s">
+      <c r="D137" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F137" t="s">
@@ -5920,10 +6618,10 @@
       <c r="C138" t="s">
         <v>465</v>
       </c>
-      <c r="D138" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E138" s="1" t="s">
+      <c r="D138" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F138" t="s">
@@ -5950,10 +6648,10 @@
       <c r="C139" t="s">
         <v>465</v>
       </c>
-      <c r="D139" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E139" s="1" t="s">
+      <c r="D139" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E139" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F139" t="s">
@@ -5980,10 +6678,10 @@
       <c r="C140" t="s">
         <v>465</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E140" s="1" t="s">
+      <c r="D140" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F140" t="s">
@@ -6010,10 +6708,10 @@
       <c r="C141" t="s">
         <v>465</v>
       </c>
-      <c r="D141" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E141" s="1" t="s">
+      <c r="D141" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E141" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F141" t="s">
@@ -6040,10 +6738,10 @@
       <c r="C142" t="s">
         <v>465</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E142" s="1" t="s">
+      <c r="D142" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E142" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F142" t="s">
@@ -6070,10 +6768,10 @@
       <c r="C143" t="s">
         <v>465</v>
       </c>
-      <c r="D143" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E143" s="1" t="s">
+      <c r="D143" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E143" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F143" t="s">
@@ -6100,10 +6798,10 @@
       <c r="C144" t="s">
         <v>465</v>
       </c>
-      <c r="D144" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E144" s="1" t="s">
+      <c r="D144" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E144" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F144" t="s">
@@ -6130,10 +6828,10 @@
       <c r="C145" t="s">
         <v>465</v>
       </c>
-      <c r="D145" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E145" s="1" t="s">
+      <c r="D145" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E145" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F145" t="s">
@@ -6160,10 +6858,10 @@
       <c r="C146" t="s">
         <v>465</v>
       </c>
-      <c r="D146" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E146" s="1" t="s">
+      <c r="D146" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F146" t="s">
@@ -6190,10 +6888,10 @@
       <c r="C147" t="s">
         <v>465</v>
       </c>
-      <c r="D147" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E147" s="1" t="s">
+      <c r="D147" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F147" t="s">
@@ -6220,10 +6918,10 @@
       <c r="C148" t="s">
         <v>465</v>
       </c>
-      <c r="D148" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E148" s="1" t="s">
+      <c r="D148" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F148" t="s">
@@ -6250,10 +6948,10 @@
       <c r="C149" t="s">
         <v>465</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E149" s="1" t="s">
+      <c r="D149" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F149" t="s">
@@ -6280,10 +6978,10 @@
       <c r="C150" t="s">
         <v>465</v>
       </c>
-      <c r="D150" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E150" s="1" t="s">
+      <c r="D150" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E150" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F150" t="s">
@@ -6310,10 +7008,10 @@
       <c r="C151" t="s">
         <v>465</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E151" s="1" t="s">
+      <c r="D151" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F151" t="s">
@@ -6340,10 +7038,10 @@
       <c r="C152" t="s">
         <v>465</v>
       </c>
-      <c r="D152" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E152" s="1" t="s">
+      <c r="D152" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F152" t="s">
@@ -6370,10 +7068,10 @@
       <c r="C153" t="s">
         <v>465</v>
       </c>
-      <c r="D153" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E153" s="1" t="s">
+      <c r="D153" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F153" t="s">
@@ -6400,10 +7098,10 @@
       <c r="C154" t="s">
         <v>465</v>
       </c>
-      <c r="D154" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E154" s="1" t="s">
+      <c r="D154" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F154" t="s">
@@ -6430,10 +7128,10 @@
       <c r="C155" t="s">
         <v>465</v>
       </c>
-      <c r="D155" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E155" s="1" t="s">
+      <c r="D155" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E155" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F155" t="s">
@@ -6460,10 +7158,10 @@
       <c r="C156" t="s">
         <v>465</v>
       </c>
-      <c r="D156" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E156" s="1" t="s">
+      <c r="D156" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E156" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F156" t="s">
@@ -6490,10 +7188,10 @@
       <c r="C157" t="s">
         <v>465</v>
       </c>
-      <c r="D157" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E157" s="1" t="s">
+      <c r="D157" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E157" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F157" t="s">
@@ -6520,10 +7218,10 @@
       <c r="C158" t="s">
         <v>465</v>
       </c>
-      <c r="D158" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E158" s="1" t="s">
+      <c r="D158" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E158" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F158" t="s">
@@ -6550,10 +7248,10 @@
       <c r="C159" t="s">
         <v>465</v>
       </c>
-      <c r="D159" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E159" s="1" t="s">
+      <c r="D159" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F159" t="s">
@@ -6580,10 +7278,10 @@
       <c r="C160" t="s">
         <v>465</v>
       </c>
-      <c r="D160" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E160" s="1" t="s">
+      <c r="D160" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E160" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F160" t="s">
@@ -6610,10 +7308,10 @@
       <c r="C161" t="s">
         <v>465</v>
       </c>
-      <c r="D161" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E161" s="1" t="s">
+      <c r="D161" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F161" t="s">
@@ -6640,10 +7338,10 @@
       <c r="C162" t="s">
         <v>465</v>
       </c>
-      <c r="D162" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E162" s="1" t="s">
+      <c r="D162" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E162" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F162" t="s">
@@ -6670,10 +7368,10 @@
       <c r="C163" t="s">
         <v>465</v>
       </c>
-      <c r="D163" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E163" s="1" t="s">
+      <c r="D163" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E163" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F163" t="s">
@@ -6700,10 +7398,10 @@
       <c r="C164" t="s">
         <v>465</v>
       </c>
-      <c r="D164" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E164" s="1" t="s">
+      <c r="D164" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E164" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F164" t="s">
@@ -6730,10 +7428,10 @@
       <c r="C165" t="s">
         <v>465</v>
       </c>
-      <c r="D165" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E165" s="1" t="s">
+      <c r="D165" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E165" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F165" t="s">
@@ -6760,10 +7458,10 @@
       <c r="C166" t="s">
         <v>465</v>
       </c>
-      <c r="D166" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E166" s="1" t="s">
+      <c r="D166" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E166" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F166" t="s">
@@ -6790,10 +7488,10 @@
       <c r="C167" t="s">
         <v>465</v>
       </c>
-      <c r="D167" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E167" s="1" t="s">
+      <c r="D167" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F167" t="s">
@@ -6820,10 +7518,10 @@
       <c r="C168" t="s">
         <v>465</v>
       </c>
-      <c r="D168" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E168" s="1" t="s">
+      <c r="D168" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E168" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F168" t="s">
@@ -6850,10 +7548,10 @@
       <c r="C169" t="s">
         <v>465</v>
       </c>
-      <c r="D169" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E169" s="1" t="s">
+      <c r="D169" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E169" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F169" t="s">
@@ -6880,10 +7578,10 @@
       <c r="C170" t="s">
         <v>465</v>
       </c>
-      <c r="D170" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E170" s="1" t="s">
+      <c r="D170" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E170" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F170" t="s">
@@ -6910,10 +7608,10 @@
       <c r="C171" t="s">
         <v>465</v>
       </c>
-      <c r="D171" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E171" s="1" t="s">
+      <c r="D171" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E171" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F171" t="s">
@@ -6940,10 +7638,10 @@
       <c r="C172" t="s">
         <v>465</v>
       </c>
-      <c r="D172" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E172" s="1" t="s">
+      <c r="D172" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E172" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F172" t="s">
@@ -6970,10 +7668,10 @@
       <c r="C173" t="s">
         <v>465</v>
       </c>
-      <c r="D173" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E173" s="1" t="s">
+      <c r="D173" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E173" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F173" t="s">
@@ -7000,10 +7698,10 @@
       <c r="C174" t="s">
         <v>465</v>
       </c>
-      <c r="D174" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E174" s="1" t="s">
+      <c r="D174" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E174" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F174" t="s">
@@ -7030,10 +7728,10 @@
       <c r="C175" t="s">
         <v>465</v>
       </c>
-      <c r="D175" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E175" s="1" t="s">
+      <c r="D175" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E175" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F175" t="s">
@@ -7060,10 +7758,10 @@
       <c r="C176" t="s">
         <v>465</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E176" s="1" t="s">
+      <c r="D176" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E176" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F176" t="s">
@@ -7090,10 +7788,10 @@
       <c r="C177" t="s">
         <v>465</v>
       </c>
-      <c r="D177" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E177" s="1" t="s">
+      <c r="D177" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E177" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F177" t="s">
@@ -7120,10 +7818,10 @@
       <c r="C178" t="s">
         <v>465</v>
       </c>
-      <c r="D178" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E178" s="1" t="s">
+      <c r="D178" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E178" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F178" t="s">
@@ -7150,10 +7848,10 @@
       <c r="C179" t="s">
         <v>465</v>
       </c>
-      <c r="D179" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E179" s="1" t="s">
+      <c r="D179" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E179" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F179" t="s">
@@ -7180,10 +7878,10 @@
       <c r="C180" t="s">
         <v>465</v>
       </c>
-      <c r="D180" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E180" s="1" t="s">
+      <c r="D180" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E180" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F180" t="s">
@@ -7210,10 +7908,10 @@
       <c r="C181" t="s">
         <v>465</v>
       </c>
-      <c r="D181" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E181" s="1" t="s">
+      <c r="D181" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E181" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F181" t="s">
@@ -7240,10 +7938,10 @@
       <c r="C182" t="s">
         <v>465</v>
       </c>
-      <c r="D182" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E182" s="1" t="s">
+      <c r="D182" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E182" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F182" t="s">
@@ -7270,10 +7968,10 @@
       <c r="C183" t="s">
         <v>465</v>
       </c>
-      <c r="D183" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E183" s="1" t="s">
+      <c r="D183" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E183" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F183" t="s">
@@ -7300,10 +7998,10 @@
       <c r="C184" t="s">
         <v>465</v>
       </c>
-      <c r="D184" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E184" s="1" t="s">
+      <c r="D184" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E184" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F184" t="s">
@@ -7330,10 +8028,10 @@
       <c r="C185" t="s">
         <v>465</v>
       </c>
-      <c r="D185" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E185" s="1" t="s">
+      <c r="D185" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F185" t="s">
@@ -7360,10 +8058,10 @@
       <c r="C186" t="s">
         <v>465</v>
       </c>
-      <c r="D186" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E186" s="1" t="s">
+      <c r="D186" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F186" t="s">
@@ -7390,10 +8088,10 @@
       <c r="C187" t="s">
         <v>465</v>
       </c>
-      <c r="D187" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E187" s="1" t="s">
+      <c r="D187" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F187" t="s">
@@ -7420,10 +8118,10 @@
       <c r="C188" t="s">
         <v>465</v>
       </c>
-      <c r="D188" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E188" s="1" t="s">
+      <c r="D188" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E188" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F188" t="s">
@@ -7450,10 +8148,10 @@
       <c r="C189" t="s">
         <v>465</v>
       </c>
-      <c r="D189" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E189" s="1" t="s">
+      <c r="D189" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E189" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F189" t="s">
@@ -7480,10 +8178,10 @@
       <c r="C190" t="s">
         <v>465</v>
       </c>
-      <c r="D190" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E190" s="1" t="s">
+      <c r="D190" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E190" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F190" t="s">
@@ -7510,10 +8208,10 @@
       <c r="C191" t="s">
         <v>465</v>
       </c>
-      <c r="D191" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E191" s="1" t="s">
+      <c r="D191" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E191" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F191" t="s">
@@ -7540,10 +8238,10 @@
       <c r="C192" t="s">
         <v>465</v>
       </c>
-      <c r="D192" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E192" s="1" t="s">
+      <c r="D192" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E192" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F192" t="s">
@@ -7570,10 +8268,10 @@
       <c r="C193" t="s">
         <v>465</v>
       </c>
-      <c r="D193" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E193" s="1" t="s">
+      <c r="D193" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E193" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F193" t="s">
@@ -7600,10 +8298,10 @@
       <c r="C194" t="s">
         <v>465</v>
       </c>
-      <c r="D194" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E194" s="1" t="s">
+      <c r="D194" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F194" t="s">
@@ -7630,10 +8328,10 @@
       <c r="C195" t="s">
         <v>465</v>
       </c>
-      <c r="D195" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E195" s="1" t="s">
+      <c r="D195" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E195" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F195" t="s">
@@ -7660,10 +8358,10 @@
       <c r="C196" t="s">
         <v>465</v>
       </c>
-      <c r="D196" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E196" s="1" t="s">
+      <c r="D196" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F196" t="s">
@@ -7690,10 +8388,10 @@
       <c r="C197" t="s">
         <v>465</v>
       </c>
-      <c r="D197" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E197" s="1" t="s">
+      <c r="D197" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E197" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F197" t="s">
@@ -7720,10 +8418,10 @@
       <c r="C198" t="s">
         <v>465</v>
       </c>
-      <c r="D198" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E198" s="1" t="s">
+      <c r="D198" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F198" t="s">
@@ -7750,10 +8448,10 @@
       <c r="C199" t="s">
         <v>465</v>
       </c>
-      <c r="D199" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E199" s="1" t="s">
+      <c r="D199" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E199" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F199" t="s">
@@ -7780,10 +8478,10 @@
       <c r="C200" t="s">
         <v>465</v>
       </c>
-      <c r="D200" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E200" s="1" t="s">
+      <c r="D200" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E200" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F200" t="s">
@@ -7810,10 +8508,10 @@
       <c r="C201" t="s">
         <v>465</v>
       </c>
-      <c r="D201" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E201" s="1" t="s">
+      <c r="D201" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E201" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F201" t="s">
@@ -7840,10 +8538,10 @@
       <c r="C202" t="s">
         <v>465</v>
       </c>
-      <c r="D202" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E202" s="1" t="s">
+      <c r="D202" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E202" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F202" t="s">
@@ -7870,10 +8568,10 @@
       <c r="C203" t="s">
         <v>465</v>
       </c>
-      <c r="D203" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E203" s="1" t="s">
+      <c r="D203" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E203" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F203" t="s">
@@ -7900,10 +8598,10 @@
       <c r="C204" t="s">
         <v>465</v>
       </c>
-      <c r="D204" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E204" s="1" t="s">
+      <c r="D204" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E204" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F204" t="s">
@@ -7930,10 +8628,10 @@
       <c r="C205" t="s">
         <v>465</v>
       </c>
-      <c r="D205" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E205" s="1" t="s">
+      <c r="D205" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E205" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F205" t="s">
@@ -7960,10 +8658,10 @@
       <c r="C206" t="s">
         <v>465</v>
       </c>
-      <c r="D206" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E206" s="1" t="s">
+      <c r="D206" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F206" t="s">
@@ -7990,10 +8688,10 @@
       <c r="C207" t="s">
         <v>465</v>
       </c>
-      <c r="D207" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E207" s="1" t="s">
+      <c r="D207" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F207" t="s">
@@ -8020,10 +8718,10 @@
       <c r="C208" t="s">
         <v>465</v>
       </c>
-      <c r="D208" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E208" s="1" t="s">
+      <c r="D208" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F208" t="s">
@@ -8050,10 +8748,10 @@
       <c r="C209" t="s">
         <v>465</v>
       </c>
-      <c r="D209" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E209" s="1" t="s">
+      <c r="D209" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F209" t="s">
@@ -8080,10 +8778,10 @@
       <c r="C210" t="s">
         <v>465</v>
       </c>
-      <c r="D210" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E210" s="1" t="s">
+      <c r="D210" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F210" t="s">
@@ -8110,10 +8808,10 @@
       <c r="C211" t="s">
         <v>465</v>
       </c>
-      <c r="D211" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E211" s="1" t="s">
+      <c r="D211" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F211" t="s">
@@ -8140,10 +8838,10 @@
       <c r="C212" t="s">
         <v>465</v>
       </c>
-      <c r="D212" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E212" s="1" t="s">
+      <c r="D212" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F212" t="s">
@@ -8170,10 +8868,10 @@
       <c r="C213" t="s">
         <v>465</v>
       </c>
-      <c r="D213" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E213" s="1" t="s">
+      <c r="D213" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F213" t="s">
@@ -8200,10 +8898,10 @@
       <c r="C214" t="s">
         <v>465</v>
       </c>
-      <c r="D214" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E214" s="1" t="s">
+      <c r="D214" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F214" t="s">
@@ -8230,10 +8928,10 @@
       <c r="C215" t="s">
         <v>465</v>
       </c>
-      <c r="D215" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E215" s="1" t="s">
+      <c r="D215" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F215" t="s">
@@ -8260,10 +8958,10 @@
       <c r="C216" t="s">
         <v>465</v>
       </c>
-      <c r="D216" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E216" s="1" t="s">
+      <c r="D216" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F216" t="s">
@@ -8290,10 +8988,10 @@
       <c r="C217" t="s">
         <v>465</v>
       </c>
-      <c r="D217" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E217" s="1" t="s">
+      <c r="D217" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F217" t="s">
@@ -8320,10 +9018,10 @@
       <c r="C218" t="s">
         <v>465</v>
       </c>
-      <c r="D218" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E218" s="1" t="s">
+      <c r="D218" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F218" t="s">
@@ -8350,10 +9048,10 @@
       <c r="C219" t="s">
         <v>465</v>
       </c>
-      <c r="D219" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E219" s="1" t="s">
+      <c r="D219" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E219" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F219" t="s">
@@ -8380,10 +9078,10 @@
       <c r="C220" t="s">
         <v>465</v>
       </c>
-      <c r="D220" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E220" s="1" t="s">
+      <c r="D220" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F220" t="s">
@@ -8410,10 +9108,10 @@
       <c r="C221" t="s">
         <v>465</v>
       </c>
-      <c r="D221" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E221" s="1" t="s">
+      <c r="D221" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E221" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F221" t="s">
@@ -8440,10 +9138,10 @@
       <c r="C222" t="s">
         <v>465</v>
       </c>
-      <c r="D222" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E222" s="1" t="s">
+      <c r="D222" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E222" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F222" t="s">
@@ -8470,10 +9168,10 @@
       <c r="C223" t="s">
         <v>465</v>
       </c>
-      <c r="D223" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E223" s="1" t="s">
+      <c r="D223" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E223" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F223" t="s">
@@ -8500,10 +9198,10 @@
       <c r="C224" t="s">
         <v>465</v>
       </c>
-      <c r="D224" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E224" s="1" t="s">
+      <c r="D224" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E224" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F224" t="s">
@@ -8530,10 +9228,10 @@
       <c r="C225" t="s">
         <v>465</v>
       </c>
-      <c r="D225" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E225" s="1" t="s">
+      <c r="D225" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E225" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F225" t="s">
@@ -8560,10 +9258,10 @@
       <c r="C226" t="s">
         <v>465</v>
       </c>
-      <c r="D226" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E226" s="1" t="s">
+      <c r="D226" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E226" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F226" t="s">
@@ -8590,10 +9288,10 @@
       <c r="C227" t="s">
         <v>465</v>
       </c>
-      <c r="D227" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E227" s="1" t="s">
+      <c r="D227" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E227" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F227" t="s">
@@ -8620,10 +9318,10 @@
       <c r="C228" t="s">
         <v>465</v>
       </c>
-      <c r="D228" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E228" s="1" t="s">
+      <c r="D228" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E228" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F228" t="s">
@@ -8650,10 +9348,10 @@
       <c r="C229" t="s">
         <v>465</v>
       </c>
-      <c r="D229" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E229" s="1" t="s">
+      <c r="D229" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E229" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F229" t="s">
@@ -8680,10 +9378,10 @@
       <c r="C230" t="s">
         <v>465</v>
       </c>
-      <c r="D230" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E230" s="1" t="s">
+      <c r="D230" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E230" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F230" t="s">
@@ -8710,10 +9408,10 @@
       <c r="C231" t="s">
         <v>465</v>
       </c>
-      <c r="D231" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E231" s="1" t="s">
+      <c r="D231" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E231" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F231" t="s">
@@ -8740,10 +9438,10 @@
       <c r="C232" t="s">
         <v>465</v>
       </c>
-      <c r="D232" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E232" s="1" t="s">
+      <c r="D232" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E232" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F232" t="s">
@@ -8770,10 +9468,10 @@
       <c r="C233" t="s">
         <v>465</v>
       </c>
-      <c r="D233" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E233" s="1" t="s">
+      <c r="D233" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E233" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F233" t="s">
@@ -8800,10 +9498,10 @@
       <c r="C234" t="s">
         <v>465</v>
       </c>
-      <c r="D234" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E234" s="1" t="s">
+      <c r="D234" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E234" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F234" t="s">
@@ -8824,4 +9522,1187 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5513FBAC-96E4-4BDF-A6C6-DF5DEEA053B5}">
+  <dimension ref="A1:A234"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="1" t="s">
+        <v>695</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>